--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.11428506869556</v>
+        <v>4.406071323663029</v>
       </c>
       <c r="D2" t="n">
-        <v>20.91516072004911</v>
+        <v>3.398713617007981</v>
       </c>
       <c r="E2" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F2" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.16671549981652</v>
+        <v>9.452091268720185</v>
       </c>
       <c r="D3" t="n">
-        <v>27.44112585097021</v>
+        <v>4.45918295078266</v>
       </c>
       <c r="E3" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F3" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.44709049817476</v>
+        <v>4.785152205953398</v>
       </c>
       <c r="D4" t="n">
-        <v>16.96807459777201</v>
+        <v>2.757312122137951</v>
       </c>
       <c r="E4" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F4" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.4930639895761</v>
+        <v>4.792622898306117</v>
       </c>
       <c r="D5" t="n">
-        <v>23.6168557042855</v>
+        <v>3.837739051946393</v>
       </c>
       <c r="E5" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F5" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.68278001322551</v>
+        <v>7.260951752149146</v>
       </c>
       <c r="D6" t="n">
-        <v>29.29423642053768</v>
+        <v>4.760313418337373</v>
       </c>
       <c r="E6" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F6" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.82097196541769</v>
+        <v>7.770907944380375</v>
       </c>
       <c r="D7" t="n">
-        <v>32.77455198831701</v>
+        <v>5.325864698101515</v>
       </c>
       <c r="E7" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F7" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.26694572530143</v>
+        <v>3.943378680361483</v>
       </c>
       <c r="D8" t="n">
-        <v>7.169848144534716</v>
+        <v>1.165100323486891</v>
       </c>
       <c r="E8" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F8" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.19619873792739</v>
+        <v>4.581882294913201</v>
       </c>
       <c r="D9" t="n">
-        <v>5.39325901278243</v>
+        <v>0.8764045895771448</v>
       </c>
       <c r="E9" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F9" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>10.6040876976889</v>
+        <v>1.723164250874446</v>
       </c>
       <c r="D10" t="n">
-        <v>33.48347857838012</v>
+        <v>5.44106526898677</v>
       </c>
       <c r="E10" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F10" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.31218703890738</v>
+        <v>3.95073039382245</v>
       </c>
       <c r="D11" t="n">
-        <v>42.17585709847086</v>
+        <v>6.853576778501516</v>
       </c>
       <c r="E11" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F11" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.72210024401951</v>
+        <v>6.29234128965317</v>
       </c>
       <c r="D12" t="n">
-        <v>4.993890849257049</v>
+        <v>0.8115072630042705</v>
       </c>
       <c r="E12" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F12" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.1852531488495</v>
+        <v>6.530103636688045</v>
       </c>
       <c r="D13" t="n">
-        <v>52.32582062267283</v>
+        <v>8.502945851184336</v>
       </c>
       <c r="E13" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F13" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>56.51596658616215</v>
+        <v>9.183844570251349</v>
       </c>
       <c r="D14" t="n">
-        <v>22.34241154369497</v>
+        <v>3.630641875850432</v>
       </c>
       <c r="E14" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F14" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>61.79290902520671</v>
+        <v>10.04134771659609</v>
       </c>
       <c r="D15" t="n">
-        <v>30.11659118563059</v>
+        <v>4.893946067664971</v>
       </c>
       <c r="E15" t="n">
-        <v>14.49266767503834</v>
+        <v>2.355058497193731</v>
       </c>
       <c r="F15" t="n">
-        <v>13.14042140109419</v>
+        <v>2.135318477677806</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
